--- a/notebooks/01_first_analysis/analisis_herramientas_completo.xlsx
+++ b/notebooks/01_first_analysis/analisis_herramientas_completo.xlsx
@@ -1659,7 +1659,7 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 1: Agentes Conversacionales</t>
         </is>
       </c>
       <c r="EL2" t="n">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 1: Agentes Conversacionales</t>
         </is>
       </c>
       <c r="EL3" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 1: Agentes Conversacionales</t>
         </is>
       </c>
       <c r="EL4" t="n">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 1: Agentes Conversacionales</t>
         </is>
       </c>
       <c r="EL5" t="n">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 1: Agentes Conversacionales</t>
         </is>
       </c>
       <c r="EL6" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 1: Agentes Conversacionales</t>
         </is>
       </c>
       <c r="EL7" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 1: Agentes Conversacionales</t>
         </is>
       </c>
       <c r="EL8" t="n">
@@ -5380,11 +5380,7 @@
       <c r="EJ9" t="n">
         <v>19</v>
       </c>
-      <c r="EK9" t="inlineStr">
-        <is>
-          <t>Modelos IA</t>
-        </is>
-      </c>
+      <c r="EK9" t="inlineStr"/>
       <c r="EL9" t="n">
         <v>13.5</v>
       </c>
@@ -5911,11 +5907,7 @@
       <c r="EJ10" t="n">
         <v>18</v>
       </c>
-      <c r="EK10" t="inlineStr">
-        <is>
-          <t>Modelos IA</t>
-        </is>
-      </c>
+      <c r="EK10" t="inlineStr"/>
       <c r="EL10" t="n">
         <v>14.5</v>
       </c>
@@ -6442,11 +6434,7 @@
       <c r="EJ11" t="n">
         <v>17</v>
       </c>
-      <c r="EK11" t="inlineStr">
-        <is>
-          <t>Modelos IA</t>
-        </is>
-      </c>
+      <c r="EK11" t="inlineStr"/>
       <c r="EL11" t="n">
         <v>13.5</v>
       </c>
@@ -6975,7 +6963,7 @@
       </c>
       <c r="EK12" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 2: Modelos Fundacionales</t>
         </is>
       </c>
       <c r="EL12" t="n">
@@ -7506,7 +7494,7 @@
       </c>
       <c r="EK13" t="inlineStr">
         <is>
-          <t>Normas UNE</t>
+          <t>Grupo 3: Norma UNE</t>
         </is>
       </c>
       <c r="EL13" t="n">
@@ -8037,7 +8025,7 @@
       </c>
       <c r="EK14" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 2: Modelos Fundacionales</t>
         </is>
       </c>
       <c r="EL14" t="n">
@@ -8568,7 +8556,7 @@
       </c>
       <c r="EK15" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 2: Modelos Fundacionales</t>
         </is>
       </c>
       <c r="EL15" t="n">
@@ -9099,7 +9087,7 @@
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 3: Norma UNE</t>
         </is>
       </c>
       <c r="EL16" t="n">
@@ -9628,11 +9616,7 @@
       <c r="EJ17" t="n">
         <v>20</v>
       </c>
-      <c r="EK17" t="inlineStr">
-        <is>
-          <t>Modelos IA</t>
-        </is>
-      </c>
+      <c r="EK17" t="inlineStr"/>
       <c r="EL17" t="n">
         <v>13.5</v>
       </c>
@@ -10161,7 +10145,7 @@
       </c>
       <c r="EK18" t="inlineStr">
         <is>
-          <t>Normas UNE</t>
+          <t>Grupo 3: Norma UNE</t>
         </is>
       </c>
       <c r="EL18" t="n">
@@ -10692,7 +10676,7 @@
       </c>
       <c r="EK19" t="inlineStr">
         <is>
-          <t>Modelos IA</t>
+          <t>Grupo 2: Modelos Fundacionales</t>
         </is>
       </c>
       <c r="EL19" t="n">

--- a/notebooks/01_first_analysis/analisis_herramientas_completo.xlsx
+++ b/notebooks/01_first_analysis/analisis_herramientas_completo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EO19"/>
+  <dimension ref="A1:EO12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,88 +1124,87 @@
       </c>
       <c r="EL1" t="inlineStr">
         <is>
-          <t>Items Cumplidos</t>
+          <t>Items Fulfilled</t>
         </is>
       </c>
       <c r="EM1" t="inlineStr">
         <is>
-          <t>Cumplimiento</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="EN1" t="inlineStr">
         <is>
-          <t>estabilidad_std</t>
+          <t>stability_std</t>
         </is>
       </c>
       <c r="EO1" t="inlineStr">
         <is>
-          <t>promedio_norm</t>
+          <t>norm_mean</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AdaptaTuTexto (Gemini 3.1 Pro)
-Facil B1</t>
+          <t>Asistente Lectura Facilitada "Francisco Javier Alvarez Jimenez"</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.017</v>
+        <v>0.1512</v>
       </c>
       <c r="C2" t="n">
-        <v>42.6044</v>
+        <v>50.644</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0424</v>
+        <v>0.1809</v>
       </c>
       <c r="E2" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6959</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6821</v>
+        <v>0.7518</v>
       </c>
       <c r="I2" t="n">
-        <v>83.9046</v>
+        <v>86.8476</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6075</v>
+        <v>0.7146</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8041</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7042</v>
+        <v>0.7594</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7168</v>
+        <v>0.7567</v>
       </c>
       <c r="P2" t="n">
-        <v>0.714</v>
+        <v>0.7769</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7154</v>
+        <v>0.7667</v>
       </c>
       <c r="R2" t="n">
-        <v>92.87430000000001</v>
+        <v>85.99460000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0097</v>
+        <v>0.0102</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9903</v>
+        <v>0.9898</v>
       </c>
       <c r="U2" t="n">
         <v>0.031</v>
@@ -1214,7 +1213,7 @@
         <v>0.046</v>
       </c>
       <c r="W2" t="n">
-        <v>0.092</v>
+        <v>0.08</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1232,7 +1231,7 @@
         <v>0.006</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="AD2" t="n">
         <v>0.002</v>
@@ -1259,7 +1258,7 @@
         <v>655</v>
       </c>
       <c r="AL2" t="n">
-        <v>218</v>
+        <v>540</v>
       </c>
       <c r="AM2" t="n">
         <v>2.241</v>
@@ -1268,7 +1267,7 @@
         <v>1.899</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.032</v>
+        <v>2.117</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -1295,7 +1294,7 @@
         <v>0.062</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.08</v>
+        <v>0.076</v>
       </c>
       <c r="AY2" t="n">
         <v>0.441</v>
@@ -1304,7 +1303,7 @@
         <v>0.344</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.546</v>
+        <v>0.396</v>
       </c>
       <c r="BB2" t="n">
         <v>1.988</v>
@@ -1313,7 +1312,7 @@
         <v>2.282</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.117</v>
+        <v>2.022</v>
       </c>
       <c r="BE2" t="n">
         <v>2.267</v>
@@ -1322,7 +1321,7 @@
         <v>2.911</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.832</v>
+        <v>2.523</v>
       </c>
       <c r="BH2" t="n">
         <v>22.276</v>
@@ -1331,7 +1330,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.381</v>
+        <v>10.588</v>
       </c>
       <c r="BK2" t="n">
         <v>1.138</v>
@@ -1340,7 +1339,7 @@
         <v>1.462</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.619</v>
+        <v>0.647</v>
       </c>
       <c r="BN2" t="n">
         <v>2.276</v>
@@ -1349,7 +1348,7 @@
         <v>2.333</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.238</v>
+        <v>2.255</v>
       </c>
       <c r="BQ2" t="n">
         <v>1.84</v>
@@ -1358,7 +1357,7 @@
         <v>0.775</v>
       </c>
       <c r="BS2" t="n">
-        <v>1</v>
+        <v>1.462</v>
       </c>
       <c r="BT2" t="n">
         <v>12.6</v>
@@ -1367,7 +1366,7 @@
         <v>2.9</v>
       </c>
       <c r="BV2" t="n">
-        <v>2.286</v>
+        <v>3.727</v>
       </c>
       <c r="BW2" t="n">
         <v>74.96943548387097</v>
@@ -1376,7 +1375,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY2" t="n">
-        <v>101.0220707732634</v>
+        <v>95.91435897435896</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -1400,7 +1399,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE2" t="n">
-        <v>97.57423110528616</v>
+        <v>92.27094017094018</v>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
@@ -1439,7 +1438,7 @@
         <v>58.38</v>
       </c>
       <c r="CN2" t="n">
-        <v>64.69</v>
+        <v>53.35</v>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
@@ -1453,7 +1452,7 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>adecuado</t>
+          <t>un poco difícil</t>
         </is>
       </c>
       <c r="CR2" t="n">
@@ -1463,7 +1462,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT2" t="n">
-        <v>45.02446483180429</v>
+        <v>41.93371794871796</v>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
@@ -1487,7 +1486,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.395293577981651</v>
+        <v>2.812814814814815</v>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
@@ -1636,7 +1635,7 @@
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>Parcialmente inadecuado</t>
+          <t>Parcialmente adecuado</t>
         </is>
       </c>
       <c r="EE2" t="n">
@@ -1646,7 +1645,7 @@
         <v>52</v>
       </c>
       <c r="EG2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="EH2" t="n">
         <v>19</v>
@@ -1655,83 +1654,82 @@
         <v>22</v>
       </c>
       <c r="EJ2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>Grupo 1: Agentes Conversacionales</t>
+          <t>Group 1: Conversational Agents</t>
         </is>
       </c>
       <c r="EL2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="EM2" t="n">
-        <v>83.333</v>
+        <v>100</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.4063885600646743</v>
+        <v>0.3185577778255009</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.4222697331958779</v>
+        <v>0.6720324441540493</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AdaptaTuTexto (Gemini 3.1 Pro)
-Muy A2</t>
+          <t>Asistente de lectura fácil “Antonio Gonzales Crespo”</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0159</v>
+        <v>0.0594</v>
       </c>
       <c r="C3" t="n">
-        <v>43.7974</v>
+        <v>46.7219</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0499</v>
+        <v>0.0716</v>
       </c>
       <c r="E3" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.7569</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6162</v>
+        <v>0.7362</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6344</v>
+        <v>0.7464</v>
       </c>
       <c r="I3" t="n">
-        <v>70.6327</v>
+        <v>86.01439999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4894</v>
+        <v>0.7196</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6548</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.7814</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0092</v>
+        <v>0.0089</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9908</v>
+        <v>0.9911</v>
       </c>
       <c r="O3" t="n">
-        <v>0.73</v>
+        <v>0.7312</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6936</v>
+        <v>0.7331</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7114</v>
+        <v>0.7321</v>
       </c>
       <c r="R3" t="n">
-        <v>85.8985</v>
+        <v>88.2561</v>
       </c>
       <c r="S3" t="n">
         <v>0.008200000000000001</v>
@@ -1746,7 +1744,7 @@
         <v>0.046</v>
       </c>
       <c r="W3" t="n">
-        <v>0.138</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -1764,7 +1762,7 @@
         <v>0.006</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AD3" t="n">
         <v>0.002</v>
@@ -1791,7 +1789,7 @@
         <v>655</v>
       </c>
       <c r="AL3" t="n">
-        <v>224</v>
+        <v>316</v>
       </c>
       <c r="AM3" t="n">
         <v>2.241</v>
@@ -1800,7 +1798,7 @@
         <v>1.899</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.858</v>
+        <v>2.081</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1827,7 +1825,7 @@
         <v>0.062</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.114</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AY3" t="n">
         <v>0.441</v>
@@ -1836,7 +1834,7 @@
         <v>0.344</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.433</v>
+        <v>0.437</v>
       </c>
       <c r="BB3" t="n">
         <v>1.988</v>
@@ -1845,7 +1843,7 @@
         <v>2.282</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.882</v>
+        <v>1.837</v>
       </c>
       <c r="BE3" t="n">
         <v>2.267</v>
@@ -1854,7 +1852,7 @@
         <v>2.911</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.309</v>
+        <v>2.29</v>
       </c>
       <c r="BH3" t="n">
         <v>22.276</v>
@@ -1863,7 +1861,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ3" t="n">
-        <v>7</v>
+        <v>12.64</v>
       </c>
       <c r="BK3" t="n">
         <v>1.138</v>
@@ -1872,7 +1870,7 @@
         <v>1.462</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.219</v>
+        <v>0.64</v>
       </c>
       <c r="BN3" t="n">
         <v>2.276</v>
@@ -1881,7 +1879,7 @@
         <v>2.333</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.062</v>
+        <v>2.08</v>
       </c>
       <c r="BQ3" t="n">
         <v>1.84</v>
@@ -1890,7 +1888,7 @@
         <v>0.775</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.4</v>
+        <v>2.154</v>
       </c>
       <c r="BT3" t="n">
         <v>12.6</v>
@@ -1899,7 +1897,7 @@
         <v>2.9</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.667</v>
+        <v>13.5</v>
       </c>
       <c r="BW3" t="n">
         <v>74.96943548387097</v>
@@ -1908,7 +1906,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY3" t="n">
-        <v>110.2732488479263</v>
+        <v>95.40289620253165</v>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
@@ -1932,7 +1930,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE3" t="n">
-        <v>106.9935685483871</v>
+        <v>91.87316455696204</v>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
@@ -1971,7 +1969,7 @@
         <v>58.38</v>
       </c>
       <c r="CN3" t="n">
-        <v>84.16</v>
+        <v>53.01</v>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
@@ -1985,7 +1983,7 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>un poco difícil</t>
         </is>
       </c>
       <c r="CR3" t="n">
@@ -1995,7 +1993,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT3" t="n">
-        <v>48.80444988479262</v>
+        <v>41.44720253164558</v>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
@@ -2019,7 +2017,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.040321428571428</v>
+        <v>3.018949367088608</v>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
@@ -2048,7 +2046,7 @@
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>Mayormente inadecuado</t>
+          <t>Inadecuado</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
@@ -2178,7 +2176,7 @@
         <v>52</v>
       </c>
       <c r="EG3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="EH3" t="n">
         <v>19</v>
@@ -2187,89 +2185,88 @@
         <v>22</v>
       </c>
       <c r="EJ3" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>Grupo 1: Agentes Conversacionales</t>
+          <t>Group 1: Conversational Agents</t>
         </is>
       </c>
       <c r="EL3" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="EM3" t="n">
-        <v>76.667</v>
+        <v>96.667</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.4011063852657864</v>
+        <v>0.3856158540135085</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.29467570432553</v>
+        <v>0.4861239730659023</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AdaptaTuTexto (Gemini 3.1 Pro)
-Sencillo B2</t>
+          <t xml:space="preserve">Asistente de lectura fácil “Mark Jonathan Camacho Escatel”: </t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0338</v>
+        <v>0.0653</v>
       </c>
       <c r="C4" t="n">
-        <v>41.8832</v>
+        <v>47.261</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0493</v>
+        <v>0.0921</v>
       </c>
       <c r="E4" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7291</v>
+        <v>0.7194</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7028</v>
+        <v>0.7212</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7157</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>85.5171</v>
+        <v>88.8728</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7181</v>
+        <v>0.5794</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6853</v>
+        <v>0.8429</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7017</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0091</v>
+        <v>0.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9909</v>
+        <v>0.99</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7382</v>
+        <v>0.734</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7367</v>
+        <v>0.7651</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.7492</v>
       </c>
       <c r="R4" t="n">
-        <v>91.9629</v>
+        <v>92.0436</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0094</v>
+        <v>0.0097</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9906</v>
+        <v>0.9903</v>
       </c>
       <c r="U4" t="n">
         <v>0.031</v>
@@ -2278,7 +2275,7 @@
         <v>0.046</v>
       </c>
       <c r="W4" t="n">
-        <v>0.091</v>
+        <v>0.075</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -2296,7 +2293,7 @@
         <v>0.006</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.038</v>
+        <v>0.006</v>
       </c>
       <c r="AD4" t="n">
         <v>0.002</v>
@@ -2323,7 +2320,7 @@
         <v>655</v>
       </c>
       <c r="AL4" t="n">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="AM4" t="n">
         <v>2.241</v>
@@ -2332,7 +2329,7 @@
         <v>1.899</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.144</v>
+        <v>2.03</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -2359,7 +2356,7 @@
         <v>0.062</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.074</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AY4" t="n">
         <v>0.441</v>
@@ -2368,7 +2365,7 @@
         <v>0.344</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.533</v>
+        <v>0.476</v>
       </c>
       <c r="BB4" t="n">
         <v>1.988</v>
@@ -2377,7 +2374,7 @@
         <v>2.282</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.191</v>
+        <v>2.012</v>
       </c>
       <c r="BE4" t="n">
         <v>2.267</v>
@@ -2386,7 +2383,7 @@
         <v>2.911</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.876</v>
+        <v>2.101</v>
       </c>
       <c r="BH4" t="n">
         <v>22.276</v>
@@ -2395,7 +2392,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.038</v>
+        <v>9.542999999999999</v>
       </c>
       <c r="BK4" t="n">
         <v>1.138</v>
@@ -2404,7 +2401,7 @@
         <v>1.462</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.731</v>
+        <v>0.657</v>
       </c>
       <c r="BN4" t="n">
         <v>2.276</v>
@@ -2413,7 +2410,7 @@
         <v>2.333</v>
       </c>
       <c r="BP4" t="n">
-        <v>2.269</v>
+        <v>2.229</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.84</v>
@@ -2422,7 +2419,7 @@
         <v>0.775</v>
       </c>
       <c r="BS4" t="n">
-        <v>1</v>
+        <v>1.529</v>
       </c>
       <c r="BT4" t="n">
         <v>12.6</v>
@@ -2431,7 +2428,7 @@
         <v>2.9</v>
       </c>
       <c r="BV4" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="BW4" t="n">
         <v>74.96943548387097</v>
@@ -2440,7 +2437,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY4" t="n">
-        <v>93.97280109074383</v>
+        <v>103.3338306244654</v>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
@@ -2464,7 +2461,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE4" t="n">
-        <v>90.37869034994698</v>
+        <v>99.9250769888794</v>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
@@ -2503,7 +2500,7 @@
         <v>58.38</v>
       </c>
       <c r="CN4" t="n">
-        <v>56.98</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
@@ -2517,7 +2514,7 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>un poco difícil</t>
+          <t>adecuado</t>
         </is>
       </c>
       <c r="CR4" t="n">
@@ -2527,7 +2524,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT4" t="n">
-        <v>41.35246932282988</v>
+        <v>43.38904191616767</v>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
@@ -2551,7 +2548,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ4" t="n">
-        <v>3.128191637630664</v>
+        <v>2.102880239520958</v>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
@@ -2700,7 +2697,7 @@
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>Parcialmente inadecuado</t>
+          <t>Parcialmente adecuado</t>
         </is>
       </c>
       <c r="EE4" t="n">
@@ -2710,7 +2707,7 @@
         <v>52</v>
       </c>
       <c r="EG4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="EH4" t="n">
         <v>19</v>
@@ -2719,89 +2716,88 @@
         <v>22</v>
       </c>
       <c r="EJ4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>Grupo 1: Agentes Conversacionales</t>
+          <t>Group 1: Conversational Agents</t>
         </is>
       </c>
       <c r="EL4" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="EM4" t="n">
-        <v>73.333</v>
+        <v>90</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.4011644948202667</v>
+        <v>0.3447398172411324</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.430176296029494</v>
+        <v>0.536325126515934</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AdaptaTuTexto (Gemini 3.1 Pro)
-Sencillo B2.1</t>
+          <t>Claude Sonnet 4.6</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0525</v>
+        <v>0.1707</v>
       </c>
       <c r="C5" t="n">
-        <v>43.0488</v>
+        <v>50.2891</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0608</v>
+        <v>0.1566</v>
       </c>
       <c r="E5" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7441</v>
+        <v>0.795</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7237</v>
+        <v>0.7832</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7338</v>
+        <v>0.7891</v>
       </c>
       <c r="I5" t="n">
-        <v>84.7406</v>
+        <v>82.491</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7539</v>
+        <v>0.7382</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8064</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7802</v>
+        <v>0.7907</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0098</v>
+        <v>0.0245</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9902</v>
+        <v>0.9755</v>
       </c>
       <c r="O5" t="n">
-        <v>0.738</v>
+        <v>0.7608</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7585</v>
+        <v>0.7842</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7481</v>
+        <v>0.7723</v>
       </c>
       <c r="R5" t="n">
-        <v>83.5842</v>
+        <v>78.5779</v>
       </c>
       <c r="S5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0276</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9724</v>
       </c>
       <c r="U5" t="n">
         <v>0.031</v>
@@ -2810,7 +2806,7 @@
         <v>0.046</v>
       </c>
       <c r="W5" t="n">
-        <v>0.079</v>
+        <v>0.037</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -2828,7 +2824,7 @@
         <v>0.006</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="AD5" t="n">
         <v>0.002</v>
@@ -2855,7 +2851,7 @@
         <v>655</v>
       </c>
       <c r="AL5" t="n">
-        <v>329</v>
+        <v>655</v>
       </c>
       <c r="AM5" t="n">
         <v>2.241</v>
@@ -2864,7 +2860,7 @@
         <v>1.899</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.08</v>
+        <v>2.053</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2891,7 +2887,7 @@
         <v>0.062</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.079</v>
+        <v>0.076</v>
       </c>
       <c r="AY5" t="n">
         <v>0.441</v>
@@ -2900,7 +2896,7 @@
         <v>0.344</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.508</v>
+        <v>0.395</v>
       </c>
       <c r="BB5" t="n">
         <v>1.988</v>
@@ -2909,7 +2905,7 @@
         <v>2.282</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.238</v>
+        <v>2.034</v>
       </c>
       <c r="BE5" t="n">
         <v>2.267</v>
@@ -2918,7 +2914,7 @@
         <v>2.911</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.97</v>
+        <v>2.529</v>
       </c>
       <c r="BH5" t="n">
         <v>22.276</v>
@@ -2927,7 +2923,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.185</v>
+        <v>18.714</v>
       </c>
       <c r="BK5" t="n">
         <v>1.138</v>
@@ -2936,7 +2932,7 @@
         <v>1.462</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.889</v>
+        <v>1.429</v>
       </c>
       <c r="BN5" t="n">
         <v>2.276</v>
@@ -2945,7 +2941,7 @@
         <v>2.333</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.222</v>
+        <v>2.457</v>
       </c>
       <c r="BQ5" t="n">
         <v>1.84</v>
@@ -2954,7 +2950,7 @@
         <v>0.775</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.056</v>
+        <v>0.978</v>
       </c>
       <c r="BT5" t="n">
         <v>12.6</v>
@@ -2963,7 +2959,7 @@
         <v>2.9</v>
       </c>
       <c r="BV5" t="n">
-        <v>2.154</v>
+        <v>3.421</v>
       </c>
       <c r="BW5" t="n">
         <v>74.96943548387097</v>
@@ -2972,7 +2968,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY5" t="n">
-        <v>95.47148176291793</v>
+        <v>90.97235896481104</v>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
@@ -2996,7 +2992,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE5" t="n">
-        <v>92.00751773049647</v>
+        <v>87.4699245950475</v>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
@@ -3035,7 +3031,7 @@
         <v>58.38</v>
       </c>
       <c r="CN5" t="n">
-        <v>60.82</v>
+        <v>54.19</v>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
@@ -3059,7 +3055,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT5" t="n">
-        <v>42.46226570415401</v>
+        <v>39.40548315025136</v>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
@@ -3083,7 +3079,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ5" t="n">
-        <v>3.05075075987842</v>
+        <v>3.441549618320612</v>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
@@ -3172,7 +3168,7 @@
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>Parcialmente inadecuado</t>
+          <t>Parcialmente adecuado</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
@@ -3232,7 +3228,7 @@
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>Parcialmente inadecuado</t>
+          <t>Parcialmente adecuado</t>
         </is>
       </c>
       <c r="EE5" t="n">
@@ -3242,7 +3238,7 @@
         <v>52</v>
       </c>
       <c r="EG5" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="EH5" t="n">
         <v>19</v>
@@ -3251,89 +3247,88 @@
         <v>22</v>
       </c>
       <c r="EJ5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>Grupo 1: Agentes Conversacionales</t>
+          <t>Group 2: Foundation Models</t>
         </is>
       </c>
       <c r="EL5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="EM5" t="n">
-        <v>80</v>
+        <v>73.333</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.3215573997844499</v>
+        <v>0.3079803388692983</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.4329156847419993</v>
+        <v>0.3960929989749037</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdaptaTuTexto (deepseek-v3.2)
-Facil B1</t>
+          <t>FACILE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1331</v>
+        <v>0.7276</v>
       </c>
       <c r="C6" t="n">
-        <v>47.1492</v>
+        <v>39.6624</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1059</v>
+        <v>0.1619</v>
       </c>
       <c r="E6" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7355</v>
+        <v>0.9281</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7347</v>
+        <v>0.9213</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7351</v>
+        <v>0.9247</v>
       </c>
       <c r="I6" t="n">
-        <v>82.5685</v>
+        <v>94.52679999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7417</v>
+        <v>0.9784</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7405</v>
+        <v>0.9275</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0163</v>
+        <v>0.0352</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9837</v>
+        <v>0.9648</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.7129</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7673</v>
+        <v>0.7399</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.75</v>
+        <v>0.7262</v>
       </c>
       <c r="R6" t="n">
-        <v>82.1721</v>
+        <v>90.827</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0159</v>
+        <v>0.0474</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9841</v>
+        <v>0.9526</v>
       </c>
       <c r="U6" t="n">
         <v>0.031</v>
@@ -3342,7 +3337,7 @@
         <v>0.046</v>
       </c>
       <c r="W6" t="n">
-        <v>0.079</v>
+        <v>0.059</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -3360,7 +3355,7 @@
         <v>0.006</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="AD6" t="n">
         <v>0.002</v>
@@ -3387,7 +3382,7 @@
         <v>655</v>
       </c>
       <c r="AL6" t="n">
-        <v>369</v>
+        <v>693</v>
       </c>
       <c r="AM6" t="n">
         <v>2.241</v>
@@ -3396,7 +3391,7 @@
         <v>1.899</v>
       </c>
       <c r="AO6" t="n">
-        <v>2.008</v>
+        <v>2.272</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -3432,7 +3427,7 @@
         <v>0.344</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.504</v>
+        <v>0.437</v>
       </c>
       <c r="BB6" t="n">
         <v>1.988</v>
@@ -3441,7 +3436,7 @@
         <v>2.282</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.223</v>
+        <v>1.963</v>
       </c>
       <c r="BE6" t="n">
         <v>2.267</v>
@@ -3450,7 +3445,7 @@
         <v>2.911</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.984</v>
+        <v>2.287</v>
       </c>
       <c r="BH6" t="n">
         <v>22.276</v>
@@ -3459,7 +3454,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.711</v>
+        <v>16.5</v>
       </c>
       <c r="BK6" t="n">
         <v>1.138</v>
@@ -3468,7 +3463,7 @@
         <v>1.462</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.711</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
         <v>2.276</v>
@@ -3477,7 +3472,7 @@
         <v>2.333</v>
       </c>
       <c r="BP6" t="n">
-        <v>2.105</v>
+        <v>2.238</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.84</v>
@@ -3486,7 +3481,7 @@
         <v>0.775</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.857</v>
+        <v>2</v>
       </c>
       <c r="BT6" t="n">
         <v>12.6</v>
@@ -3495,7 +3490,7 @@
         <v>2.9</v>
       </c>
       <c r="BV6" t="n">
-        <v>3.727</v>
+        <v>6.111</v>
       </c>
       <c r="BW6" t="n">
         <v>74.96943548387097</v>
@@ -3504,7 +3499,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY6" t="n">
-        <v>94.62153732446416</v>
+        <v>80.92556589147287</v>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
@@ -3518,7 +3513,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>muy fácil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="CC6" t="n">
@@ -3528,7 +3523,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE6" t="n">
-        <v>90.97567504311407</v>
+        <v>76.997419250646</v>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
@@ -3542,22 +3537,22 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
+          <t>bastante fácil</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>bastante fácil</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
           <t>muy fácil</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CJ6" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>muy fácil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="CL6" t="n">
@@ -3567,7 +3562,7 @@
         <v>58.38</v>
       </c>
       <c r="CN6" t="n">
-        <v>57.54</v>
+        <v>45.42</v>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
@@ -3581,7 +3576,7 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>un poco difícil</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="CR6" t="n">
@@ -3591,7 +3586,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT6" t="n">
-        <v>43.25953436807096</v>
+        <v>35.79394702842378</v>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
@@ -3615,7 +3610,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.992728997289974</v>
+        <v>4.261604651162791</v>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
@@ -3764,7 +3759,7 @@
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>Parcialmente inadecuado</t>
+          <t>Parcialmente adecuado</t>
         </is>
       </c>
       <c r="EE6" t="n">
@@ -3774,7 +3769,7 @@
         <v>52</v>
       </c>
       <c r="EG6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="EH6" t="n">
         <v>19</v>
@@ -3783,11 +3778,11 @@
         <v>22</v>
       </c>
       <c r="EJ6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>Grupo 1: Agentes Conversacionales</t>
+          <t>Group 3: UNE Standard</t>
         </is>
       </c>
       <c r="EL6" t="n">
@@ -3797,75 +3792,74 @@
         <v>93.333</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.2201390865421199</v>
+        <v>0.4367833884739029</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.4981751245348797</v>
+        <v>0.5212817704440919</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AdaptaTuTexto (deepseek-v3.2)
-Muy A2</t>
+          <t>GPT 5.4 Think</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1071</v>
+        <v>0.1754</v>
       </c>
       <c r="C7" t="n">
-        <v>48.8119</v>
+        <v>50.1571</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1213</v>
+        <v>0.1673</v>
       </c>
       <c r="E7" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.729</v>
+        <v>0.8118</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7167</v>
+        <v>0.7985</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7228</v>
+        <v>0.8051</v>
       </c>
       <c r="I7" t="n">
-        <v>73.0818</v>
+        <v>94.0719</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6752</v>
+        <v>0.7236</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5226</v>
+        <v>0.8796</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5989</v>
+        <v>0.8016</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0125</v>
       </c>
       <c r="N7" t="n">
-        <v>0.991</v>
+        <v>0.9875</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7527</v>
+        <v>0.7575</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7679</v>
+        <v>0.7832</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7602</v>
+        <v>0.7702</v>
       </c>
       <c r="R7" t="n">
-        <v>84.15940000000001</v>
+        <v>93.8518</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0095</v>
+        <v>0.0153</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9905</v>
+        <v>0.9847</v>
       </c>
       <c r="U7" t="n">
         <v>0.031</v>
@@ -3874,7 +3868,7 @@
         <v>0.046</v>
       </c>
       <c r="W7" t="n">
-        <v>0.13</v>
+        <v>0.061</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -3892,7 +3886,7 @@
         <v>0.006</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.016</v>
+        <v>0.026</v>
       </c>
       <c r="AD7" t="n">
         <v>0.002</v>
@@ -3919,7 +3913,7 @@
         <v>655</v>
       </c>
       <c r="AL7" t="n">
-        <v>386</v>
+        <v>661</v>
       </c>
       <c r="AM7" t="n">
         <v>2.241</v>
@@ -3928,7 +3922,7 @@
         <v>1.899</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.858</v>
+        <v>2.076</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3955,7 +3949,7 @@
         <v>0.062</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.074</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AY7" t="n">
         <v>0.441</v>
@@ -3964,7 +3958,7 @@
         <v>0.344</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.391</v>
+        <v>0.351</v>
       </c>
       <c r="BB7" t="n">
         <v>1.988</v>
@@ -3973,7 +3967,7 @@
         <v>2.282</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.109</v>
+        <v>2.053</v>
       </c>
       <c r="BE7" t="n">
         <v>2.267</v>
@@ -3982,7 +3976,7 @@
         <v>2.911</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.556</v>
+        <v>2.849</v>
       </c>
       <c r="BH7" t="n">
         <v>22.276</v>
@@ -3991,7 +3985,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ7" t="n">
-        <v>6.772</v>
+        <v>16.122</v>
       </c>
       <c r="BK7" t="n">
         <v>1.138</v>
@@ -4000,7 +3994,7 @@
         <v>1.462</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.333</v>
+        <v>1.244</v>
       </c>
       <c r="BN7" t="n">
         <v>2.276</v>
@@ -4009,7 +4003,7 @@
         <v>2.333</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.035</v>
+        <v>2.268</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.84</v>
@@ -4018,7 +4012,7 @@
         <v>0.775</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.071</v>
+        <v>1</v>
       </c>
       <c r="BT7" t="n">
         <v>12.6</v>
@@ -4027,7 +4021,7 @@
         <v>2.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>2.182</v>
+        <v>4.077</v>
       </c>
       <c r="BW7" t="n">
         <v>74.96943548387097</v>
@@ -4036,7 +4030,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY7" t="n">
-        <v>106.4579528790693</v>
+        <v>89.72181818181818</v>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
@@ -4050,7 +4044,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>muy fácil</t>
+          <t>fácil</t>
         </is>
       </c>
       <c r="CC7" t="n">
@@ -4060,7 +4054,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE7" t="n">
-        <v>103.0354008211947</v>
+        <v>86.11378787878789</v>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
@@ -4099,7 +4093,7 @@
         <v>58.38</v>
       </c>
       <c r="CN7" t="n">
-        <v>76.79000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
@@ -4113,7 +4107,7 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>un poco fácil</t>
+          <t>un poco difícil</t>
         </is>
       </c>
       <c r="CR7" t="n">
@@ -4123,7 +4117,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT7" t="n">
-        <v>47.79472577964611</v>
+        <v>39.89212121212122</v>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
@@ -4147,7 +4141,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.369424870466322</v>
+        <v>3.541484848484847</v>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
@@ -4176,7 +4170,7 @@
       </c>
       <c r="DF7" t="inlineStr">
         <is>
-          <t>Mayormente inadecuado</t>
+          <t>Inadecuado</t>
         </is>
       </c>
       <c r="DG7" t="inlineStr">
@@ -4236,7 +4230,7 @@
       </c>
       <c r="DR7" t="inlineStr">
         <is>
-          <t>Parcialmente inadecuado</t>
+          <t>Parcialmente adecuado</t>
         </is>
       </c>
       <c r="DS7" t="inlineStr">
@@ -4315,11 +4309,11 @@
         <v>22</v>
       </c>
       <c r="EJ7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>Grupo 1: Agentes Conversacionales</t>
+          <t>Group 2: Foundation Models</t>
         </is>
       </c>
       <c r="EL7" t="n">
@@ -4329,75 +4323,74 @@
         <v>83.333</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.3176655115524456</v>
+        <v>0.2779923184022218</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.5075435443097005</v>
+        <v>0.7001293829780103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AdaptaTuTexto (deepseek-v3.2)
-Sencillo B2</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2329</v>
+        <v>0.0625</v>
       </c>
       <c r="C8" t="n">
-        <v>46.2219</v>
+        <v>49.3049</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1051</v>
+        <v>0.1324</v>
       </c>
       <c r="E8" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8134</v>
+        <v>0.6933</v>
       </c>
       <c r="G8" t="n">
-        <v>0.801</v>
+        <v>0.6752</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8072</v>
+        <v>0.6841</v>
       </c>
       <c r="I8" t="n">
-        <v>82.7504</v>
+        <v>79.6245</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.5145</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7867</v>
+        <v>0.7579</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6362</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0179</v>
+        <v>0.0126</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9821</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.746</v>
+        <v>0.7588</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7881</v>
+        <v>0.7667</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7665</v>
+        <v>0.7627</v>
       </c>
       <c r="R8" t="n">
-        <v>86.22499999999999</v>
+        <v>89.8177</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0179</v>
+        <v>0.0103</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9821</v>
+        <v>0.9897</v>
       </c>
       <c r="U8" t="n">
         <v>0.031</v>
@@ -4406,7 +4399,7 @@
         <v>0.046</v>
       </c>
       <c r="W8" t="n">
-        <v>0.063</v>
+        <v>0.076</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -4424,7 +4417,7 @@
         <v>0.006</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.061</v>
+        <v>0.016</v>
       </c>
       <c r="AD8" t="n">
         <v>0.002</v>
@@ -4433,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -4451,7 +4444,7 @@
         <v>655</v>
       </c>
       <c r="AL8" t="n">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="AM8" t="n">
         <v>2.241</v>
@@ -4460,7 +4453,7 @@
         <v>1.899</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.21</v>
+        <v>1.968</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -4487,7 +4480,7 @@
         <v>0.062</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="AY8" t="n">
         <v>0.441</v>
@@ -4496,7 +4489,7 @@
         <v>0.344</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.519</v>
+        <v>0.373</v>
       </c>
       <c r="BB8" t="n">
         <v>1.988</v>
@@ -4505,7 +4498,7 @@
         <v>2.282</v>
       </c>
       <c r="BD8" t="n">
-        <v>2</v>
+        <v>2.207</v>
       </c>
       <c r="BE8" t="n">
         <v>2.267</v>
@@ -4514,7 +4507,7 @@
         <v>2.911</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.925</v>
+        <v>2.683</v>
       </c>
       <c r="BH8" t="n">
         <v>22.276</v>
@@ -4523,7 +4516,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12.118</v>
+        <v>11.2</v>
       </c>
       <c r="BK8" t="n">
         <v>1.138</v>
@@ -4532,7 +4525,7 @@
         <v>1.462</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.824</v>
+        <v>0.875</v>
       </c>
       <c r="BN8" t="n">
         <v>2.276</v>
@@ -4541,7 +4534,7 @@
         <v>2.333</v>
       </c>
       <c r="BP8" t="n">
-        <v>2.235</v>
+        <v>2.225</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.84</v>
@@ -4550,7 +4543,7 @@
         <v>0.775</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.316</v>
+        <v>1.071</v>
       </c>
       <c r="BT8" t="n">
         <v>12.6</v>
@@ -4559,7 +4552,7 @@
         <v>2.9</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.1</v>
+        <v>2.769</v>
       </c>
       <c r="BW8" t="n">
         <v>74.96943548387097</v>
@@ -4568,7 +4561,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY8" t="n">
-        <v>86.04284671532848</v>
+        <v>101.0071341463415</v>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
@@ -4582,7 +4575,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>muy fácil</t>
         </is>
       </c>
       <c r="CC8" t="n">
@@ -4592,7 +4585,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE8" t="n">
-        <v>82.12170387863176</v>
+        <v>97.59098323170734</v>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
@@ -4621,7 +4614,7 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>fácil</t>
+          <t>muy fácil</t>
         </is>
       </c>
       <c r="CL8" t="n">
@@ -4631,7 +4624,7 @@
         <v>58.38</v>
       </c>
       <c r="CN8" t="n">
-        <v>46.5</v>
+        <v>65.27</v>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
@@ -4645,7 +4638,7 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>difícil</t>
+          <t>adecuado</t>
         </is>
       </c>
       <c r="CR8" t="n">
@@ -4655,7 +4648,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT8" t="n">
-        <v>37.01729282954058</v>
+        <v>45.82025261324043</v>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
@@ -4679,7 +4672,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ8" t="n">
-        <v>3.75528710462287</v>
+        <v>2.449696428571429</v>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
@@ -4828,7 +4821,7 @@
       </c>
       <c r="ED8" t="inlineStr">
         <is>
-          <t>Parcialmente inadecuado</t>
+          <t>Parcialmente adecuado</t>
         </is>
       </c>
       <c r="EE8" t="n">
@@ -4838,7 +4831,7 @@
         <v>52</v>
       </c>
       <c r="EG8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="EH8" t="n">
         <v>19</v>
@@ -4847,88 +4840,88 @@
         <v>22</v>
       </c>
       <c r="EJ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>Grupo 1: Agentes Conversacionales</t>
+          <t>Group 2: Foundation Models</t>
         </is>
       </c>
       <c r="EL8" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="EM8" t="n">
-        <v>100</v>
+        <v>76.667</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.2046507248733437</v>
+        <v>0.3821666255109876</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.5895080348376641</v>
+        <v>0.4553311873517535</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Asistente Lectura Facilitada "Francisco Javier Alvarez Jimenez"</t>
+          <t>Modelo_Qwen3.5_9B</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1512</v>
+        <v>0.1341</v>
       </c>
       <c r="C9" t="n">
-        <v>50.644</v>
+        <v>44.6969</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1809</v>
+        <v>0.0814</v>
       </c>
       <c r="E9" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7736</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.7307</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7518</v>
+        <v>0.7516</v>
       </c>
       <c r="I9" t="n">
-        <v>86.8476</v>
+        <v>90.37090000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7146</v>
+        <v>0.8434</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8041</v>
+        <v>0.8235</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7594</v>
+        <v>0.8335</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01</v>
+        <v>0.0103</v>
       </c>
       <c r="N9" t="n">
-        <v>0.99</v>
+        <v>0.9897</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7567</v>
+        <v>0.7429</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7769</v>
+        <v>0.7452</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7667</v>
+        <v>0.7441</v>
       </c>
       <c r="R9" t="n">
-        <v>85.99460000000001</v>
+        <v>87.8921</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0102</v>
+        <v>0.0123</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9898</v>
+        <v>0.9877</v>
       </c>
       <c r="U9" t="n">
         <v>0.031</v>
@@ -4937,7 +4930,7 @@
         <v>0.046</v>
       </c>
       <c r="W9" t="n">
-        <v>0.08</v>
+        <v>0.067</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -4955,7 +4948,7 @@
         <v>0.006</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.011</v>
+        <v>0.028</v>
       </c>
       <c r="AD9" t="n">
         <v>0.002</v>
@@ -4982,7 +4975,7 @@
         <v>655</v>
       </c>
       <c r="AL9" t="n">
-        <v>540</v>
+        <v>608</v>
       </c>
       <c r="AM9" t="n">
         <v>2.241</v>
@@ -4991,7 +4984,7 @@
         <v>1.899</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.117</v>
+        <v>1.97</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5018,7 +5011,7 @@
         <v>0.062</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.076</v>
+        <v>0.068</v>
       </c>
       <c r="AY9" t="n">
         <v>0.441</v>
@@ -5027,7 +5020,7 @@
         <v>0.344</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.396</v>
+        <v>0.387</v>
       </c>
       <c r="BB9" t="n">
         <v>1.988</v>
@@ -5036,7 +5029,7 @@
         <v>2.282</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.022</v>
+        <v>2.403</v>
       </c>
       <c r="BE9" t="n">
         <v>2.267</v>
@@ -5045,7 +5038,7 @@
         <v>2.911</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.523</v>
+        <v>2.587</v>
       </c>
       <c r="BH9" t="n">
         <v>22.276</v>
@@ -5054,7 +5047,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.588</v>
+        <v>12.16</v>
       </c>
       <c r="BK9" t="n">
         <v>1.138</v>
@@ -5063,7 +5056,7 @@
         <v>1.462</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.647</v>
+        <v>0.76</v>
       </c>
       <c r="BN9" t="n">
         <v>2.276</v>
@@ -5072,7 +5065,7 @@
         <v>2.333</v>
       </c>
       <c r="BP9" t="n">
-        <v>2.255</v>
+        <v>2.16</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.84</v>
@@ -5081,7 +5074,7 @@
         <v>0.775</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.462</v>
+        <v>1.385</v>
       </c>
       <c r="BT9" t="n">
         <v>12.6</v>
@@ -5090,7 +5083,7 @@
         <v>2.9</v>
       </c>
       <c r="BV9" t="n">
-        <v>3.727</v>
+        <v>2.1</v>
       </c>
       <c r="BW9" t="n">
         <v>74.96943548387097</v>
@@ -5099,7 +5092,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY9" t="n">
-        <v>95.91435897435896</v>
+        <v>96.10649424126086</v>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
@@ -5123,7 +5116,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE9" t="n">
-        <v>92.27094017094018</v>
+        <v>92.58762005792417</v>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
@@ -5162,7 +5155,7 @@
         <v>58.38</v>
       </c>
       <c r="CN9" t="n">
-        <v>53.35</v>
+        <v>52.2</v>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
@@ -5186,7 +5179,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT9" t="n">
-        <v>41.93371794871796</v>
+        <v>44.82043847241867</v>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
@@ -5210,7 +5203,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.812814814814815</v>
+        <v>2.948445544554456</v>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
@@ -5378,84 +5371,88 @@
         <v>22</v>
       </c>
       <c r="EJ9" t="n">
-        <v>19</v>
-      </c>
-      <c r="EK9" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>Group 3: UNE Standard</t>
+        </is>
+      </c>
       <c r="EL9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="EM9" t="n">
-        <v>90</v>
+        <v>93.333</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.2682102175402401</v>
+        <v>0.3178395777650641</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.6749869815875524</v>
+        <v>0.5088267764091003</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Asistente de lectura fácil “Antonio Gonzales Crespo”</t>
+          <t>Placea</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0594</v>
+        <v>0.0867</v>
       </c>
       <c r="C10" t="n">
-        <v>46.7219</v>
+        <v>42.1956</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0716</v>
+        <v>0.0789</v>
       </c>
       <c r="E10" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7569</v>
+        <v>0.7687</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7362</v>
+        <v>0.7443</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7464</v>
+        <v>0.7563</v>
       </c>
       <c r="I10" t="n">
-        <v>86.01439999999999</v>
+        <v>87.97669999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7196</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8678</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7814</v>
+        <v>0.7839</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0089</v>
+        <v>0.0108</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9911</v>
+        <v>0.9892</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7312</v>
+        <v>0.7338</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7331</v>
+        <v>0.7512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7321</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>88.2561</v>
+        <v>90.3143</v>
       </c>
       <c r="S10" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0108</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9918</v>
+        <v>0.9892</v>
       </c>
       <c r="U10" t="n">
         <v>0.031</v>
@@ -5464,7 +5461,7 @@
         <v>0.046</v>
       </c>
       <c r="W10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -5482,7 +5479,7 @@
         <v>0.006</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.006</v>
+        <v>0.042</v>
       </c>
       <c r="AD10" t="n">
         <v>0.002</v>
@@ -5509,7 +5506,7 @@
         <v>655</v>
       </c>
       <c r="AL10" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AM10" t="n">
         <v>2.241</v>
@@ -5518,7 +5515,7 @@
         <v>1.899</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.081</v>
+        <v>1.9</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5545,7 +5542,7 @@
         <v>0.062</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="AY10" t="n">
         <v>0.441</v>
@@ -5554,7 +5551,7 @@
         <v>0.344</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.437</v>
+        <v>0.45</v>
       </c>
       <c r="BB10" t="n">
         <v>1.988</v>
@@ -5563,7 +5560,7 @@
         <v>2.282</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.837</v>
+        <v>2.389</v>
       </c>
       <c r="BE10" t="n">
         <v>2.267</v>
@@ -5572,7 +5569,7 @@
         <v>2.911</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="BH10" t="n">
         <v>22.276</v>
@@ -5581,7 +5578,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12.64</v>
+        <v>11.179</v>
       </c>
       <c r="BK10" t="n">
         <v>1.138</v>
@@ -5590,7 +5587,7 @@
         <v>1.462</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="BN10" t="n">
         <v>2.276</v>
@@ -5599,7 +5596,7 @@
         <v>2.333</v>
       </c>
       <c r="BP10" t="n">
-        <v>2.08</v>
+        <v>2.179</v>
       </c>
       <c r="BQ10" t="n">
         <v>1.84</v>
@@ -5608,7 +5605,7 @@
         <v>0.775</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.154</v>
+        <v>1.562</v>
       </c>
       <c r="BT10" t="n">
         <v>12.6</v>
@@ -5617,7 +5614,7 @@
         <v>2.9</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.5</v>
+        <v>2.909</v>
       </c>
       <c r="BW10" t="n">
         <v>74.96943548387097</v>
@@ -5626,7 +5623,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY10" t="n">
-        <v>95.40289620253165</v>
+        <v>101.3628043178686</v>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
@@ -5650,7 +5647,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE10" t="n">
-        <v>91.87316455696204</v>
+        <v>97.9709439595774</v>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
@@ -5689,7 +5686,7 @@
         <v>58.38</v>
       </c>
       <c r="CN10" t="n">
-        <v>53.01</v>
+        <v>56.55</v>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
@@ -5713,7 +5710,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT10" t="n">
-        <v>41.44720253164558</v>
+        <v>46.61764469453377</v>
       </c>
       <c r="CU10" t="inlineStr">
         <is>
@@ -5737,7 +5734,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ10" t="n">
-        <v>3.018949367088608</v>
+        <v>2.436086816720259</v>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
@@ -5905,84 +5902,88 @@
         <v>22</v>
       </c>
       <c r="EJ10" t="n">
-        <v>18</v>
-      </c>
-      <c r="EK10" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>Group 1: Conversational Agents</t>
+        </is>
+      </c>
       <c r="EL10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="EM10" t="n">
-        <v>96.667</v>
+        <v>90</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.3340613459183713</v>
+        <v>0.3396612465022376</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.5559416554700281</v>
+        <v>0.4705210862541721</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asistente de lectura fácil “Mark Jonathan Camacho Escatel”: </t>
+          <t>SimpleText (ClearText)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0653</v>
+        <v>0.8188</v>
       </c>
       <c r="C11" t="n">
-        <v>47.261</v>
+        <v>41.0793</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0921</v>
+        <v>0.1701</v>
       </c>
       <c r="E11" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7194</v>
+        <v>0.948</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7212</v>
+        <v>0.9512</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.9496</v>
       </c>
       <c r="I11" t="n">
-        <v>88.8728</v>
+        <v>94.5266</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5794</v>
+        <v>0.9899</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8429</v>
+        <v>0.8983</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01</v>
+        <v>0.0202</v>
       </c>
       <c r="N11" t="n">
-        <v>0.99</v>
+        <v>0.9798</v>
       </c>
       <c r="O11" t="n">
-        <v>0.734</v>
+        <v>0.7016</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7651</v>
+        <v>0.7412</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7492</v>
+        <v>0.7208</v>
       </c>
       <c r="R11" t="n">
-        <v>92.0436</v>
+        <v>87.5685</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0097</v>
+        <v>0.0301</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9903</v>
+        <v>0.9699</v>
       </c>
       <c r="U11" t="n">
         <v>0.031</v>
@@ -5991,7 +5992,7 @@
         <v>0.046</v>
       </c>
       <c r="W11" t="n">
-        <v>0.075</v>
+        <v>0.038</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -6009,7 +6010,7 @@
         <v>0.006</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.006</v>
+        <v>0.04</v>
       </c>
       <c r="AD11" t="n">
         <v>0.002</v>
@@ -6018,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -6036,7 +6037,7 @@
         <v>655</v>
       </c>
       <c r="AL11" t="n">
-        <v>334</v>
+        <v>692</v>
       </c>
       <c r="AM11" t="n">
         <v>2.241</v>
@@ -6045,7 +6046,7 @@
         <v>1.899</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.03</v>
+        <v>2.226</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -6072,7 +6073,7 @@
         <v>0.062</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="AY11" t="n">
         <v>0.441</v>
@@ -6081,7 +6082,7 @@
         <v>0.344</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.476</v>
+        <v>0.435</v>
       </c>
       <c r="BB11" t="n">
         <v>1.988</v>
@@ -6090,7 +6091,7 @@
         <v>2.282</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.012</v>
+        <v>1.966</v>
       </c>
       <c r="BE11" t="n">
         <v>2.267</v>
@@ -6099,7 +6100,7 @@
         <v>2.911</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.101</v>
+        <v>2.299</v>
       </c>
       <c r="BH11" t="n">
         <v>22.276</v>
@@ -6108,7 +6109,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.542999999999999</v>
+        <v>20.97</v>
       </c>
       <c r="BK11" t="n">
         <v>1.138</v>
@@ -6117,7 +6118,7 @@
         <v>1.462</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.657</v>
+        <v>1.061</v>
       </c>
       <c r="BN11" t="n">
         <v>2.276</v>
@@ -6126,7 +6127,7 @@
         <v>2.333</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.229</v>
+        <v>2.273</v>
       </c>
       <c r="BQ11" t="n">
         <v>1.84</v>
@@ -6135,7 +6136,7 @@
         <v>0.775</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.529</v>
+        <v>1.667</v>
       </c>
       <c r="BT11" t="n">
         <v>12.6</v>
@@ -6144,7 +6145,7 @@
         <v>2.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>2.3</v>
+        <v>12.4</v>
       </c>
       <c r="BW11" t="n">
         <v>74.96943548387097</v>
@@ -6153,7 +6154,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY11" t="n">
-        <v>103.3338306244654</v>
+        <v>78.49647703072711</v>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
@@ -6167,7 +6168,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>muy fácil</t>
+          <t>algo fácil</t>
         </is>
       </c>
       <c r="CC11" t="n">
@@ -6177,7 +6178,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE11" t="n">
-        <v>99.9250769888794</v>
+        <v>74.64788408883481</v>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
@@ -6191,22 +6192,22 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
+          <t>bastante fácil</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>bastante fácil</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
           <t>muy fácil</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CJ11" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
         </is>
       </c>
       <c r="CL11" t="n">
@@ -6216,7 +6217,7 @@
         <v>58.38</v>
       </c>
       <c r="CN11" t="n">
-        <v>69.65000000000001</v>
+        <v>44.95</v>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
@@ -6230,7 +6231,7 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>adecuado</t>
+          <t>difícil</t>
         </is>
       </c>
       <c r="CR11" t="n">
@@ -6240,7 +6241,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT11" t="n">
-        <v>43.38904191616767</v>
+        <v>36.13513081837542</v>
       </c>
       <c r="CU11" t="inlineStr">
         <is>
@@ -6264,7 +6265,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.102880239520958</v>
+        <v>4.431728323699422</v>
       </c>
       <c r="DA11" t="inlineStr">
         <is>
@@ -6353,7 +6354,7 @@
       </c>
       <c r="DR11" t="inlineStr">
         <is>
-          <t>Parcialmente inadecuado</t>
+          <t>Parcialmente adecuado</t>
         </is>
       </c>
       <c r="DS11" t="inlineStr">
@@ -6423,7 +6424,7 @@
         <v>52</v>
       </c>
       <c r="EG11" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="EH11" t="n">
         <v>19</v>
@@ -6432,84 +6433,88 @@
         <v>22</v>
       </c>
       <c r="EJ11" t="n">
-        <v>17</v>
-      </c>
-      <c r="EK11" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="EK11" t="inlineStr">
+        <is>
+          <t>Group 3: UNE Standard</t>
+        </is>
+      </c>
       <c r="EL11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="EM11" t="n">
-        <v>90</v>
+        <v>83.333</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.3049470517414289</v>
+        <v>0.3700561378057017</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.5934285114058417</v>
+        <v>0.5941870518400698</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1707</v>
+        <v>0.1627</v>
       </c>
       <c r="C12" t="n">
-        <v>50.2891</v>
+        <v>53.3765</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1566</v>
+        <v>0.1857</v>
       </c>
       <c r="E12" t="n">
         <v>98.61239999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.795</v>
+        <v>0.777</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7832</v>
+        <v>0.7461</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7891</v>
+        <v>0.7612</v>
       </c>
       <c r="I12" t="n">
-        <v>82.491</v>
+        <v>84.5235</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7382</v>
+        <v>0.7551</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.851</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7907</v>
+        <v>0.803</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0245</v>
+        <v>0.0105</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9755</v>
+        <v>0.9895</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7608</v>
+        <v>0.7749</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7842</v>
+        <v>0.7966</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7723</v>
+        <v>0.7856</v>
       </c>
       <c r="R12" t="n">
-        <v>78.5779</v>
+        <v>91.02209999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0276</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9724</v>
+        <v>0.9901</v>
       </c>
       <c r="U12" t="n">
         <v>0.031</v>
@@ -6518,7 +6523,7 @@
         <v>0.046</v>
       </c>
       <c r="W12" t="n">
-        <v>0.037</v>
+        <v>0.108</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -6536,7 +6541,7 @@
         <v>0.006</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="AD12" t="n">
         <v>0.002</v>
@@ -6563,7 +6568,7 @@
         <v>655</v>
       </c>
       <c r="AL12" t="n">
-        <v>655</v>
+        <v>685</v>
       </c>
       <c r="AM12" t="n">
         <v>2.241</v>
@@ -6572,7 +6577,7 @@
         <v>1.899</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.053</v>
+        <v>1.949</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6599,7 +6604,7 @@
         <v>0.062</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.076</v>
+        <v>0.078</v>
       </c>
       <c r="AY12" t="n">
         <v>0.441</v>
@@ -6608,7 +6613,7 @@
         <v>0.344</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.395</v>
+        <v>0.359</v>
       </c>
       <c r="BB12" t="n">
         <v>1.988</v>
@@ -6617,7 +6622,7 @@
         <v>2.282</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.034</v>
+        <v>2.231</v>
       </c>
       <c r="BE12" t="n">
         <v>2.267</v>
@@ -6626,7 +6631,7 @@
         <v>2.911</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.529</v>
+        <v>2.785</v>
       </c>
       <c r="BH12" t="n">
         <v>22.276</v>
@@ -6635,7 +6640,7 @@
         <v>16.795</v>
       </c>
       <c r="BJ12" t="n">
-        <v>18.714</v>
+        <v>8.457000000000001</v>
       </c>
       <c r="BK12" t="n">
         <v>1.138</v>
@@ -6644,7 +6649,7 @@
         <v>1.462</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.429</v>
+        <v>0.444</v>
       </c>
       <c r="BN12" t="n">
         <v>2.276</v>
@@ -6653,7 +6658,7 @@
         <v>2.333</v>
       </c>
       <c r="BP12" t="n">
-        <v>2.457</v>
+        <v>2.173</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.84</v>
@@ -6662,7 +6667,7 @@
         <v>0.775</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.978</v>
+        <v>2.067</v>
       </c>
       <c r="BT12" t="n">
         <v>12.6</v>
@@ -6671,7 +6676,7 @@
         <v>2.9</v>
       </c>
       <c r="BV12" t="n">
-        <v>3.421</v>
+        <v>2.15</v>
       </c>
       <c r="BW12" t="n">
         <v>74.96943548387097</v>
@@ -6680,7 +6685,7 @@
         <v>93.80803937324228</v>
       </c>
       <c r="BY12" t="n">
-        <v>90.97235896481104</v>
+        <v>100.5396966537113</v>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
@@ -6704,7 +6709,7 @@
         <v>90.48884491763764</v>
       </c>
       <c r="CE12" t="n">
-        <v>87.4699245950475</v>
+        <v>96.98561143236327</v>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
@@ -6743,7 +6748,7 @@
         <v>58.38</v>
       </c>
       <c r="CN12" t="n">
-        <v>54.19</v>
+        <v>60.53</v>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
@@ -6767,7 +6772,7 @@
         <v>44.07321213338691</v>
       </c>
       <c r="CT12" t="n">
-        <v>39.40548315025136</v>
+        <v>46.56008626410087</v>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
@@ -6791,7 +6796,7 @@
         <v>3.198801526717557</v>
       </c>
       <c r="CZ12" t="n">
-        <v>3.441549618320612</v>
+        <v>2.228766423357664</v>
       </c>
       <c r="DA12" t="inlineStr">
         <is>
@@ -6820,7 +6825,7 @@
       </c>
       <c r="DF12" t="inlineStr">
         <is>
-          <t>Inadecuado</t>
+          <t>Mayormente inadecuado</t>
         </is>
       </c>
       <c r="DG12" t="inlineStr">
@@ -6880,7 +6885,7 @@
       </c>
       <c r="DR12" t="inlineStr">
         <is>
-          <t>Parcialmente adecuado</t>
+          <t>Parcialmente inadecuado</t>
         </is>
       </c>
       <c r="DS12" t="inlineStr">
@@ -6959,3737 +6964,24 @@
         <v>22</v>
       </c>
       <c r="EJ12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="EK12" t="inlineStr">
         <is>
-          <t>Grupo 2: Modelos Fundacionales</t>
+          <t>Group 2: Foundation Models</t>
         </is>
       </c>
       <c r="EL12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="EM12" t="n">
-        <v>93.333</v>
+        <v>80</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.2742225328751096</v>
+        <v>0.368827885993098</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.5234381324994364</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>FACILE</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.7276</v>
-      </c>
-      <c r="C13" t="n">
-        <v>39.6624</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.1619</v>
-      </c>
-      <c r="E13" t="n">
-        <v>98.61239999999999</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.9281</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.9213</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.9247</v>
-      </c>
-      <c r="I13" t="n">
-        <v>94.52679999999999</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.9784</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.8764999999999999</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.9275</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.0352</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.9648</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.7129</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.7399</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.7262</v>
-      </c>
-      <c r="R13" t="n">
-        <v>90.827</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.0474</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.9526</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>646</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>655</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>693</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>2.241</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.899</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>2.272</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.988</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.282</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>1.963</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.267</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.911</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.287</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>22.276</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>16.795</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1.138</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>2.276</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>2.238</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>6.111</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>74.96943548387097</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>93.80803937324228</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>80.92556589147287</v>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>algo fácil</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="CC13" t="n">
-        <v>71.12952620967744</v>
-      </c>
-      <c r="CD13" t="n">
-        <v>90.48884491763764</v>
-      </c>
-      <c r="CE13" t="n">
-        <v>76.997419250646</v>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CH13" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CI13" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CJ13" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CK13" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="CL13" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>45.42</v>
-      </c>
-      <c r="CO13" t="inlineStr">
-        <is>
-          <t>difícil</t>
-        </is>
-      </c>
-      <c r="CP13" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CQ13" t="inlineStr">
-        <is>
-          <t>difícil</t>
-        </is>
-      </c>
-      <c r="CR13" t="n">
-        <v>34.0179435483871</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>44.07321213338691</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>35.79394702842378</v>
-      </c>
-      <c r="CU13" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CV13" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CW13" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CX13" t="n">
-        <v>4.649718750000002</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>3.198801526717557</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>4.261604651162791</v>
-      </c>
-      <c r="DA13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DB13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DC13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DD13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DE13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DF13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DG13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DH13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DI13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DJ13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DK13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DL13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DM13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DN13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DO13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DP13" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DQ13" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DR13" t="inlineStr">
-        <is>
-          <t>Parcialmente inadecuado</t>
-        </is>
-      </c>
-      <c r="DS13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DT13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DU13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DV13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DW13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DX13" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DY13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DZ13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EA13" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EB13" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EC13" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="ED13" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EE13" t="n">
-        <v>52</v>
-      </c>
-      <c r="EF13" t="n">
-        <v>52</v>
-      </c>
-      <c r="EG13" t="n">
-        <v>50</v>
-      </c>
-      <c r="EH13" t="n">
-        <v>19</v>
-      </c>
-      <c r="EI13" t="n">
-        <v>22</v>
-      </c>
-      <c r="EJ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="EK13" t="inlineStr">
-        <is>
-          <t>Grupo 3: Norma UNE</t>
-        </is>
-      </c>
-      <c r="EL13" t="n">
-        <v>14</v>
-      </c>
-      <c r="EM13" t="n">
-        <v>93.333</v>
-      </c>
-      <c r="EN13" t="n">
-        <v>0.4303270298090234</v>
-      </c>
-      <c r="EO13" t="n">
-        <v>0.5392743526405162</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>GPT 5.4 Think</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.1754</v>
-      </c>
-      <c r="C14" t="n">
-        <v>50.1571</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.1673</v>
-      </c>
-      <c r="E14" t="n">
-        <v>98.61239999999999</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.8118</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.7985</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.8051</v>
-      </c>
-      <c r="I14" t="n">
-        <v>94.0719</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.7236</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.8796</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.8016</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.9875</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.7575</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.7832</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.7702</v>
-      </c>
-      <c r="R14" t="n">
-        <v>93.8518</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.0153</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.9847</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>646</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>655</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>661</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>2.241</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.899</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>2.076</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.988</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.282</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>2.053</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.267</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.911</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.849</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>22.276</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>16.795</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>16.122</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.138</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.244</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>2.276</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>2.268</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>4.077</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>74.96943548387097</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>93.80803937324228</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>89.72181818181818</v>
-      </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>algo fácil</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>fácil</t>
-        </is>
-      </c>
-      <c r="CC14" t="n">
-        <v>71.12952620967744</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>90.48884491763764</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>86.11378787878789</v>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CH14" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CI14" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CJ14" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CK14" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CL14" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="CO14" t="inlineStr">
-        <is>
-          <t>difícil</t>
-        </is>
-      </c>
-      <c r="CP14" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CQ14" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CR14" t="n">
-        <v>34.0179435483871</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>44.07321213338691</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>39.89212121212122</v>
-      </c>
-      <c r="CU14" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CV14" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CW14" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CX14" t="n">
-        <v>4.649718750000002</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>3.198801526717557</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>3.541484848484847</v>
-      </c>
-      <c r="DA14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DB14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DC14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DD14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DE14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DF14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DG14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DH14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DI14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DJ14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DK14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DL14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DM14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DN14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DO14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DP14" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DQ14" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DR14" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DS14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DT14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DU14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DV14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DW14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DX14" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DY14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DZ14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EA14" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EB14" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EC14" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="ED14" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EE14" t="n">
-        <v>52</v>
-      </c>
-      <c r="EF14" t="n">
-        <v>52</v>
-      </c>
-      <c r="EG14" t="n">
-        <v>52</v>
-      </c>
-      <c r="EH14" t="n">
-        <v>19</v>
-      </c>
-      <c r="EI14" t="n">
-        <v>22</v>
-      </c>
-      <c r="EJ14" t="n">
-        <v>18</v>
-      </c>
-      <c r="EK14" t="inlineStr">
-        <is>
-          <t>Grupo 2: Modelos Fundacionales</t>
-        </is>
-      </c>
-      <c r="EL14" t="n">
-        <v>14</v>
-      </c>
-      <c r="EM14" t="n">
-        <v>93.333</v>
-      </c>
-      <c r="EN14" t="n">
-        <v>0.2349828051856575</v>
-      </c>
-      <c r="EO14" t="n">
-        <v>0.7582463444694716</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Pro</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="C15" t="n">
-        <v>49.3049</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.1324</v>
-      </c>
-      <c r="E15" t="n">
-        <v>98.61239999999999</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.6933</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.6752</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.6841</v>
-      </c>
-      <c r="I15" t="n">
-        <v>79.6245</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.5145</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.7579</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.6362</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.9874000000000001</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.7588</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.7667</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.7627</v>
-      </c>
-      <c r="R15" t="n">
-        <v>89.8177</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.0103</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.9897</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>646</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>655</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>448</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>2.241</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.899</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1.968</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.988</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.282</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>2.207</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2.267</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>2.911</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.683</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>22.276</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>16.795</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.138</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>2.276</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>2.225</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>2.769</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>74.96943548387097</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>93.80803937324228</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>101.0071341463415</v>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>algo fácil</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CC15" t="n">
-        <v>71.12952620967744</v>
-      </c>
-      <c r="CD15" t="n">
-        <v>90.48884491763764</v>
-      </c>
-      <c r="CE15" t="n">
-        <v>97.59098323170734</v>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CH15" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CI15" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CJ15" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CK15" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CL15" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>65.27</v>
-      </c>
-      <c r="CO15" t="inlineStr">
-        <is>
-          <t>difícil</t>
-        </is>
-      </c>
-      <c r="CP15" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CQ15" t="inlineStr">
-        <is>
-          <t>adecuado</t>
-        </is>
-      </c>
-      <c r="CR15" t="n">
-        <v>34.0179435483871</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>44.07321213338691</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>45.82025261324043</v>
-      </c>
-      <c r="CU15" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CV15" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CW15" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CX15" t="n">
-        <v>4.649718750000002</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>3.198801526717557</v>
-      </c>
-      <c r="CZ15" t="n">
-        <v>2.449696428571429</v>
-      </c>
-      <c r="DA15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DB15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DC15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DD15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DE15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DF15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DG15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DH15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DI15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DJ15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DK15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DL15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DM15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DN15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DO15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DP15" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DQ15" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DR15" t="inlineStr">
-        <is>
-          <t>Parcialmente inadecuado</t>
-        </is>
-      </c>
-      <c r="DS15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DT15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DU15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DV15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DW15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DX15" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DY15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DZ15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EA15" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EB15" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EC15" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="ED15" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EE15" t="n">
-        <v>52</v>
-      </c>
-      <c r="EF15" t="n">
-        <v>52</v>
-      </c>
-      <c r="EG15" t="n">
-        <v>50</v>
-      </c>
-      <c r="EH15" t="n">
-        <v>19</v>
-      </c>
-      <c r="EI15" t="n">
-        <v>22</v>
-      </c>
-      <c r="EJ15" t="n">
-        <v>18</v>
-      </c>
-      <c r="EK15" t="inlineStr">
-        <is>
-          <t>Grupo 2: Modelos Fundacionales</t>
-        </is>
-      </c>
-      <c r="EL15" t="n">
-        <v>13</v>
-      </c>
-      <c r="EM15" t="n">
-        <v>86.667</v>
-      </c>
-      <c r="EN15" t="n">
-        <v>0.2911796201390596</v>
-      </c>
-      <c r="EO15" t="n">
-        <v>0.5656217980850727</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Modelo_Qwen3.5_9B</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.1341</v>
-      </c>
-      <c r="C16" t="n">
-        <v>44.6969</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.0814</v>
-      </c>
-      <c r="E16" t="n">
-        <v>98.61239999999999</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.7736</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.7307</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.7516</v>
-      </c>
-      <c r="I16" t="n">
-        <v>90.37090000000001</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.8434</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.8335</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.0103</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.9897</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.7429</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.7452</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.7441</v>
-      </c>
-      <c r="R16" t="n">
-        <v>87.8921</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.9877</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>646</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>655</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>608</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>2.241</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.899</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.988</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.282</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>2.403</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>2.267</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.911</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.587</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>22.276</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>16.795</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.138</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>2.276</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>74.96943548387097</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>93.80803937324228</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>96.10649424126086</v>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>algo fácil</t>
-        </is>
-      </c>
-      <c r="CA16" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CC16" t="n">
-        <v>71.12952620967744</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>90.48884491763764</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>92.58762005792417</v>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CH16" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CI16" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CJ16" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CK16" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CL16" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="CO16" t="inlineStr">
-        <is>
-          <t>difícil</t>
-        </is>
-      </c>
-      <c r="CP16" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CQ16" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CR16" t="n">
-        <v>34.0179435483871</v>
-      </c>
-      <c r="CS16" t="n">
-        <v>44.07321213338691</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>44.82043847241867</v>
-      </c>
-      <c r="CU16" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CV16" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CW16" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CX16" t="n">
-        <v>4.649718750000002</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>3.198801526717557</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>2.948445544554456</v>
-      </c>
-      <c r="DA16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DB16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DC16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DD16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DE16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DF16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DG16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DH16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DI16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DJ16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DK16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DL16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DM16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DN16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DO16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DP16" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DQ16" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DR16" t="inlineStr">
-        <is>
-          <t>Parcialmente inadecuado</t>
-        </is>
-      </c>
-      <c r="DS16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DT16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DU16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DV16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DW16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DX16" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DY16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DZ16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EA16" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EB16" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EC16" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="ED16" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EE16" t="n">
-        <v>52</v>
-      </c>
-      <c r="EF16" t="n">
-        <v>52</v>
-      </c>
-      <c r="EG16" t="n">
-        <v>50</v>
-      </c>
-      <c r="EH16" t="n">
-        <v>19</v>
-      </c>
-      <c r="EI16" t="n">
-        <v>22</v>
-      </c>
-      <c r="EJ16" t="n">
-        <v>14</v>
-      </c>
-      <c r="EK16" t="inlineStr">
-        <is>
-          <t>Grupo 3: Norma UNE</t>
-        </is>
-      </c>
-      <c r="EL16" t="n">
-        <v>12</v>
-      </c>
-      <c r="EM16" t="n">
-        <v>80</v>
-      </c>
-      <c r="EN16" t="n">
-        <v>0.2885182763177131</v>
-      </c>
-      <c r="EO16" t="n">
-        <v>0.512707194704298</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Placea</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.0867</v>
-      </c>
-      <c r="C17" t="n">
-        <v>42.1956</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.0789</v>
-      </c>
-      <c r="E17" t="n">
-        <v>98.61239999999999</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.7687</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.7443</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.7563</v>
-      </c>
-      <c r="I17" t="n">
-        <v>87.97669999999999</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.7000999999999999</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.8678</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.7839</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.0108</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.9892</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.7338</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.7512</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.7423999999999999</v>
-      </c>
-      <c r="R17" t="n">
-        <v>90.3143</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.0108</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.9892</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>646</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>655</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>313</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>2.241</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.899</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.988</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.282</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>2.389</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2.267</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.911</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>22.276</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>16.795</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>11.179</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.138</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>2.276</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>2.179</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.562</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>2.909</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>74.96943548387097</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>93.80803937324228</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>101.3628043178686</v>
-      </c>
-      <c r="BZ17" t="inlineStr">
-        <is>
-          <t>algo fácil</t>
-        </is>
-      </c>
-      <c r="CA17" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CC17" t="n">
-        <v>71.12952620967744</v>
-      </c>
-      <c r="CD17" t="n">
-        <v>90.48884491763764</v>
-      </c>
-      <c r="CE17" t="n">
-        <v>97.9709439595774</v>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CH17" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CI17" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CJ17" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CK17" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CL17" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="CM17" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="CN17" t="n">
-        <v>56.55</v>
-      </c>
-      <c r="CO17" t="inlineStr">
-        <is>
-          <t>difícil</t>
-        </is>
-      </c>
-      <c r="CP17" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CQ17" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CR17" t="n">
-        <v>34.0179435483871</v>
-      </c>
-      <c r="CS17" t="n">
-        <v>44.07321213338691</v>
-      </c>
-      <c r="CT17" t="n">
-        <v>46.61764469453377</v>
-      </c>
-      <c r="CU17" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CV17" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CW17" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CX17" t="n">
-        <v>4.649718750000002</v>
-      </c>
-      <c r="CY17" t="n">
-        <v>3.198801526717557</v>
-      </c>
-      <c r="CZ17" t="n">
-        <v>2.436086816720259</v>
-      </c>
-      <c r="DA17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DB17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DC17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DD17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DE17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DF17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DG17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DH17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DI17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DJ17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DK17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DL17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DM17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DN17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DO17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DP17" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DQ17" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DR17" t="inlineStr">
-        <is>
-          <t>Parcialmente inadecuado</t>
-        </is>
-      </c>
-      <c r="DS17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DT17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DU17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DV17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DW17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DX17" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DY17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DZ17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EA17" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EB17" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EC17" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="ED17" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EE17" t="n">
-        <v>52</v>
-      </c>
-      <c r="EF17" t="n">
-        <v>52</v>
-      </c>
-      <c r="EG17" t="n">
-        <v>50</v>
-      </c>
-      <c r="EH17" t="n">
-        <v>19</v>
-      </c>
-      <c r="EI17" t="n">
-        <v>22</v>
-      </c>
-      <c r="EJ17" t="n">
-        <v>20</v>
-      </c>
-      <c r="EK17" t="inlineStr"/>
-      <c r="EL17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="EM17" t="n">
-        <v>90</v>
-      </c>
-      <c r="EN17" t="n">
-        <v>0.3070821723506336</v>
-      </c>
-      <c r="EO17" t="n">
-        <v>0.5312834218489592</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SimpleText (ClearText)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.8188</v>
-      </c>
-      <c r="C18" t="n">
-        <v>41.0793</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.1701</v>
-      </c>
-      <c r="E18" t="n">
-        <v>98.61239999999999</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.9512</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.9496</v>
-      </c>
-      <c r="I18" t="n">
-        <v>94.5266</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.9899</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.8983</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.9441000000000001</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.0202</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.9798</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.7016</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.7412</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.7208</v>
-      </c>
-      <c r="R18" t="n">
-        <v>87.5685</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.0301</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.9699</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>646</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>655</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>692</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>2.241</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.899</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>2.226</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.988</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.282</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.966</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.267</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.911</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.299</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>22.276</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>16.795</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>20.97</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.138</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.061</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>2.276</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>2.273</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>74.96943548387097</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>93.80803937324228</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>78.49647703072711</v>
-      </c>
-      <c r="BZ18" t="inlineStr">
-        <is>
-          <t>algo fácil</t>
-        </is>
-      </c>
-      <c r="CA18" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>algo fácil</t>
-        </is>
-      </c>
-      <c r="CC18" t="n">
-        <v>71.12952620967744</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>90.48884491763764</v>
-      </c>
-      <c r="CE18" t="n">
-        <v>74.64788408883481</v>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CH18" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CI18" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CJ18" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CK18" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CL18" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="CN18" t="n">
-        <v>44.95</v>
-      </c>
-      <c r="CO18" t="inlineStr">
-        <is>
-          <t>difícil</t>
-        </is>
-      </c>
-      <c r="CP18" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CQ18" t="inlineStr">
-        <is>
-          <t>difícil</t>
-        </is>
-      </c>
-      <c r="CR18" t="n">
-        <v>34.0179435483871</v>
-      </c>
-      <c r="CS18" t="n">
-        <v>44.07321213338691</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>36.13513081837542</v>
-      </c>
-      <c r="CU18" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CV18" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CW18" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CX18" t="n">
-        <v>4.649718750000002</v>
-      </c>
-      <c r="CY18" t="n">
-        <v>3.198801526717557</v>
-      </c>
-      <c r="CZ18" t="n">
-        <v>4.431728323699422</v>
-      </c>
-      <c r="DA18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DB18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DC18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DD18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DE18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DF18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DG18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DH18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DI18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DJ18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DK18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DL18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DM18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DN18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DO18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DP18" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DQ18" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DR18" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DS18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DT18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DU18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DV18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DW18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DX18" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DY18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DZ18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EA18" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EB18" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EC18" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="ED18" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EE18" t="n">
-        <v>52</v>
-      </c>
-      <c r="EF18" t="n">
-        <v>52</v>
-      </c>
-      <c r="EG18" t="n">
-        <v>52</v>
-      </c>
-      <c r="EH18" t="n">
-        <v>19</v>
-      </c>
-      <c r="EI18" t="n">
-        <v>22</v>
-      </c>
-      <c r="EJ18" t="n">
-        <v>20</v>
-      </c>
-      <c r="EK18" t="inlineStr">
-        <is>
-          <t>Grupo 3: Norma UNE</t>
-        </is>
-      </c>
-      <c r="EL18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="EM18" t="n">
-        <v>96.667</v>
-      </c>
-      <c r="EN18" t="n">
-        <v>0.3498762992554095</v>
-      </c>
-      <c r="EO18" t="n">
-        <v>0.6596438602128034</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>deepseek-v3.2</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.1627</v>
-      </c>
-      <c r="C19" t="n">
-        <v>53.3765</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1857</v>
-      </c>
-      <c r="E19" t="n">
-        <v>98.61239999999999</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.777</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.7461</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.7612</v>
-      </c>
-      <c r="I19" t="n">
-        <v>84.5235</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.7551</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.803</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.0105</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.9895</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.7749</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.7966</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.7856</v>
-      </c>
-      <c r="R19" t="n">
-        <v>91.02209999999999</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.009900000000000001</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.9901</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>646</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>655</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>685</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>2.241</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.899</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1.949</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.988</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.282</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.231</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.267</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.911</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.785</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>22.276</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>16.795</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>8.457000000000001</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>1.138</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>2.276</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>2.173</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>2.067</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>74.96943548387097</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>93.80803937324228</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>100.5396966537113</v>
-      </c>
-      <c r="BZ19" t="inlineStr">
-        <is>
-          <t>algo fácil</t>
-        </is>
-      </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CC19" t="n">
-        <v>71.12952620967744</v>
-      </c>
-      <c r="CD19" t="n">
-        <v>90.48884491763764</v>
-      </c>
-      <c r="CE19" t="n">
-        <v>96.98561143236327</v>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CH19" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CI19" t="inlineStr">
-        <is>
-          <t>bastante fácil</t>
-        </is>
-      </c>
-      <c r="CJ19" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CK19" t="inlineStr">
-        <is>
-          <t>muy fácil</t>
-        </is>
-      </c>
-      <c r="CL19" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="CN19" t="n">
-        <v>60.53</v>
-      </c>
-      <c r="CO19" t="inlineStr">
-        <is>
-          <t>difícil</t>
-        </is>
-      </c>
-      <c r="CP19" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CQ19" t="inlineStr">
-        <is>
-          <t>un poco difícil</t>
-        </is>
-      </c>
-      <c r="CR19" t="n">
-        <v>34.0179435483871</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>44.07321213338691</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>46.56008626410087</v>
-      </c>
-      <c r="CU19" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CV19" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CW19" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="CX19" t="n">
-        <v>4.649718750000002</v>
-      </c>
-      <c r="CY19" t="n">
-        <v>3.198801526717557</v>
-      </c>
-      <c r="CZ19" t="n">
-        <v>2.228766423357664</v>
-      </c>
-      <c r="DA19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DB19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DC19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DD19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DE19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DF19" t="inlineStr">
-        <is>
-          <t>Mayormente inadecuado</t>
-        </is>
-      </c>
-      <c r="DG19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DH19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DI19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DJ19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DK19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DL19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DM19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DN19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DO19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DP19" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DQ19" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="DR19" t="inlineStr">
-        <is>
-          <t>Parcialmente inadecuado</t>
-        </is>
-      </c>
-      <c r="DS19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DT19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DU19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DV19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DW19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DX19" t="inlineStr">
-        <is>
-          <t>Inadecuado</t>
-        </is>
-      </c>
-      <c r="DY19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="DZ19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EA19" t="inlineStr">
-        <is>
-          <t>Adecuado</t>
-        </is>
-      </c>
-      <c r="EB19" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EC19" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="ED19" t="inlineStr">
-        <is>
-          <t>Parcialmente adecuado</t>
-        </is>
-      </c>
-      <c r="EE19" t="n">
-        <v>52</v>
-      </c>
-      <c r="EF19" t="n">
-        <v>52</v>
-      </c>
-      <c r="EG19" t="n">
-        <v>52</v>
-      </c>
-      <c r="EH19" t="n">
-        <v>19</v>
-      </c>
-      <c r="EI19" t="n">
-        <v>22</v>
-      </c>
-      <c r="EJ19" t="n">
-        <v>19</v>
-      </c>
-      <c r="EK19" t="inlineStr">
-        <is>
-          <t>Grupo 2: Modelos Fundacionales</t>
-        </is>
-      </c>
-      <c r="EL19" t="n">
-        <v>14</v>
-      </c>
-      <c r="EM19" t="n">
-        <v>93.333</v>
-      </c>
-      <c r="EN19" t="n">
-        <v>0.2866630069459555</v>
-      </c>
-      <c r="EO19" t="n">
-        <v>0.7626993038489339</v>
+        <v>0.6715706900218524</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/01_first_analysis/analisis_herramientas_completo.xlsx
+++ b/notebooks/01_first_analysis/analisis_herramientas_completo.xlsx
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="EL2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="EM2" t="n">
-        <v>100</v>
+        <v>86.667</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.3185577778255009</v>
+        <v>0.2842303091606552</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.6720324441540493</v>
+        <v>0.6515941062416063</v>
       </c>
     </row>
     <row r="3">
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="EL3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="EM3" t="n">
-        <v>96.667</v>
+        <v>93.333</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.3856158540135085</v>
+        <v>0.3847019839046188</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.4861239730659023</v>
+        <v>0.5152437366123078</v>
       </c>
     </row>
     <row r="4">
@@ -2724,16 +2724,16 @@
         </is>
       </c>
       <c r="EL4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="EM4" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.3447398172411324</v>
+        <v>0.3560382939968362</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.536325126515934</v>
+        <v>0.5671133252470847</v>
       </c>
     </row>
     <row r="5">
@@ -3255,16 +3255,16 @@
         </is>
       </c>
       <c r="EL5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="EM5" t="n">
-        <v>73.333</v>
+        <v>93.333</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.3079803388692983</v>
+        <v>0.3100958423921303</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.3960929989749037</v>
+        <v>0.4971079350151025</v>
       </c>
     </row>
     <row r="6">
@@ -3792,10 +3792,10 @@
         <v>93.333</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.4367833884739029</v>
+        <v>0.455462139248744</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.5212817704440919</v>
+        <v>0.5050707157986412</v>
       </c>
     </row>
     <row r="7">
@@ -4317,16 +4317,16 @@
         </is>
       </c>
       <c r="EL7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="EM7" t="n">
-        <v>83.333</v>
+        <v>93.333</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.2779923184022218</v>
+        <v>0.2697181161238288</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.7001293829780103</v>
+        <v>0.7345368369700467</v>
       </c>
     </row>
     <row r="8">
@@ -4848,16 +4848,16 @@
         </is>
       </c>
       <c r="EL8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="EM8" t="n">
-        <v>76.667</v>
+        <v>80</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.3821666255109876</v>
+        <v>0.3673872877332308</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.4553311873517535</v>
+        <v>0.5305407749762505</v>
       </c>
     </row>
     <row r="9">
@@ -5379,16 +5379,16 @@
         </is>
       </c>
       <c r="EL9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="EM9" t="n">
-        <v>93.333</v>
+        <v>66.667</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.3178395777650641</v>
+        <v>0.3350956677929117</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.5088267764091003</v>
+        <v>0.4589088546391809</v>
       </c>
     </row>
     <row r="10">
@@ -5910,16 +5910,16 @@
         </is>
       </c>
       <c r="EL10" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="EM10" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.3396612465022376</v>
+        <v>0.3478590791260158</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.4705210862541721</v>
+        <v>0.5002634567949098</v>
       </c>
     </row>
     <row r="11">
@@ -6441,16 +6441,16 @@
         </is>
       </c>
       <c r="EL11" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="EM11" t="n">
-        <v>83.333</v>
+        <v>93.333</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.3700561378057017</v>
+        <v>0.4125633224440607</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.5941870518400698</v>
+        <v>0.5969886550765551</v>
       </c>
     </row>
     <row r="12">
@@ -6972,16 +6972,16 @@
         </is>
       </c>
       <c r="EL12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="EM12" t="n">
-        <v>80</v>
+        <v>93.333</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.368827885993098</v>
+        <v>0.3339621580072221</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.6715706900218524</v>
+        <v>0.7590371168313065</v>
       </c>
     </row>
   </sheetData>
